--- a/diseases/d019/2000-2004.xlsx
+++ b/diseases/d019/2000-2004.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -3085,9 +3082,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3481,9 +3475,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -3777,9 +3768,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4073,9 +4061,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4369,9 +4354,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -4665,9 +4647,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -4961,9 +4940,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -5257,9 +5233,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -5553,9 +5526,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -5849,9 +5819,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -6145,9 +6112,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -6441,9 +6405,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6737,9 +6698,6 @@
       <c r="O41" t="n">
         <v>1</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.002125693624458129</v>
       </c>
@@ -7033,9 +6991,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -7429,9 +7384,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -7725,9 +7677,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -8021,9 +7970,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -8317,9 +8263,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -8613,9 +8556,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -8909,9 +8849,6 @@
       <c r="O55" t="n">
         <v>1</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -9205,9 +9142,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -9501,9 +9435,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -9797,9 +9728,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -10093,9 +10021,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -10389,9 +10314,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -10685,9 +10607,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -10981,9 +10900,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -11377,9 +11293,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -11673,9 +11586,6 @@
       <c r="O73" t="n">
         <v>1</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -11969,9 +11879,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -12265,9 +12172,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -12561,9 +12465,6 @@
       <c r="O79" t="n">
         <v>1</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -12857,9 +12758,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -13153,9 +13051,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -13449,9 +13344,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -13745,9 +13637,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -14041,9 +13930,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -14337,9 +14223,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -14633,9 +14516,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -14929,9 +14809,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -15325,9 +15202,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -15621,9 +15495,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -15917,9 +15788,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -16213,9 +16081,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -16509,9 +16374,6 @@
       <c r="O105" t="n">
         <v>1</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -16805,9 +16667,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -17101,9 +16960,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -17397,9 +17253,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -17693,9 +17546,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -17989,9 +17839,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -18285,9 +18132,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -18579,9 +18423,6 @@
         <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">

--- a/diseases/d019/2000-2004.xlsx
+++ b/diseases/d019/2000-2004.xlsx
@@ -721,12 +721,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -760,84 +760,95 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>0.003237104677897888</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -864,17 +875,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -908,22 +919,39 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -931,6 +959,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN3" t="b">
+        <v>1</v>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -948,7 +1034,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
@@ -961,42 +1047,42 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1023,17 +1109,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1072,165 +1158,79 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Hundaæði</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN4" t="b">
-        <v>1</v>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2000-02-01</t>
+          <t>2000-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2000-02</t>
+          <t>2000-01</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1306,79 +1306,170 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Hundaæði</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN5" t="b">
+        <v>0</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_RABI_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1531,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2000-03-01</t>
+          <t>2000-02-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2000-03</t>
+          <t>2000-02</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1588,12 +1679,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2000-04-01</t>
+          <t>2000-03-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2000-04</t>
+          <t>2000-03</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1736,12 +1827,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2000-05-01</t>
+          <t>2000-04-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2000-05</t>
+          <t>2000-04</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1884,12 +1975,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2000-06-01</t>
+          <t>2000-05-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2000-06</t>
+          <t>2000-05</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -2032,12 +2123,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2000-07-01</t>
+          <t>2000-06-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2000-07</t>
+          <t>2000-06</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2180,12 +2271,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2000-08-01</t>
+          <t>2000-07-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2000-08</t>
+          <t>2000-07</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2328,12 +2419,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2000-09-01</t>
+          <t>2000-08-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2000-09</t>
+          <t>2000-08</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2476,12 +2567,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2000-10-01</t>
+          <t>2000-09-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2000-10</t>
+          <t>2000-09</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2624,12 +2715,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2000-11-01</t>
+          <t>2000-10-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2000-11</t>
+          <t>2000-10</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2772,12 +2863,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2000-12-01</t>
+          <t>2000-11-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2000-12</t>
+          <t>2000-11</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2920,12 +3011,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2000-12-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2001-01</t>
+          <t>2000-12</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -3038,12 +3129,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3092,7 +3183,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -3117,7 +3208,7 @@
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
         </is>
       </c>
       <c r="AT17" t="n">
@@ -3130,42 +3221,42 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3197,12 +3288,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3243,22 +3334,22 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_HISTORY</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Hundaæði</t>
+          <t>Rabies</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -3268,7 +3359,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>national_registry_notifications</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3283,7 +3374,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -3308,7 +3399,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>active</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
@@ -3318,12 +3409,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>IS_DOH_historical_registry_annual</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -3351,7 +3442,7 @@
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
         </is>
       </c>
       <c r="AT18" t="n">
@@ -3364,42 +3455,42 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3431,12 +3522,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3473,6 +3564,9 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
@@ -3509,42 +3603,42 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -3571,17 +3665,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3606,12 +3700,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2001-02-01</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2001-02</t>
+          <t>2001-01</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -3620,79 +3714,170 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Hundaæði</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN20" t="b">
+        <v>0</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_RABI_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -3754,12 +3939,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2001-02-01</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2001-02</t>
+          <t>2001-01</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -3899,12 +4084,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2001-03-01</t>
+          <t>2001-02-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2001-03</t>
+          <t>2001-02</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -4047,12 +4232,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2001-03-01</t>
+          <t>2001-02-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2001-03</t>
+          <t>2001-02</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -4192,12 +4377,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2001-04-01</t>
+          <t>2001-03-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2001-04</t>
+          <t>2001-03</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -4340,12 +4525,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2001-04-01</t>
+          <t>2001-03-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2001-04</t>
+          <t>2001-03</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4485,12 +4670,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2001-05-01</t>
+          <t>2001-04-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2001-05</t>
+          <t>2001-04</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -4633,12 +4818,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2001-05-01</t>
+          <t>2001-04-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2001-05</t>
+          <t>2001-04</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -4778,12 +4963,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2001-06-01</t>
+          <t>2001-05-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2001-06</t>
+          <t>2001-05</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -4926,12 +5111,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2001-06-01</t>
+          <t>2001-05-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2001-06</t>
+          <t>2001-05</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -5071,12 +5256,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2001-07-01</t>
+          <t>2001-06-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2001-07</t>
+          <t>2001-06</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -5219,12 +5404,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2001-07-01</t>
+          <t>2001-06-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2001-07</t>
+          <t>2001-06</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -5364,12 +5549,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2001-08-01</t>
+          <t>2001-07-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2001-08</t>
+          <t>2001-07</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -5512,12 +5697,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2001-08-01</t>
+          <t>2001-07-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2001-08</t>
+          <t>2001-07</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5657,12 +5842,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2001-09-01</t>
+          <t>2001-08-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2001-09</t>
+          <t>2001-08</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -5805,12 +5990,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2001-09-01</t>
+          <t>2001-08-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2001-09</t>
+          <t>2001-08</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -5950,25 +6135,25 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2001-10-01</t>
+          <t>2001-09-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2001-10</t>
+          <t>2001-09</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>0.01476180680677245</v>
+        <v>0</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -6098,12 +6283,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2001-10-01</t>
+          <t>2001-09-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2001-10</t>
+          <t>2001-09</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -6243,25 +6428,25 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2001-11-01</t>
+          <t>2001-10-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2001-11</t>
+          <t>2001-10</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>0.01476180680677245</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -6391,12 +6576,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2001-11-01</t>
+          <t>2001-10-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2001-11</t>
+          <t>2001-10</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -6536,12 +6721,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2001-12-01</t>
+          <t>2001-11-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2001-12</t>
+          <t>2001-11</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -6684,22 +6869,22 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2001-12-01</t>
+          <t>2001-11-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2001-12</t>
+          <t>2001-11</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0.002125693624458129</v>
+        <v>0</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -6829,12 +7014,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2001-12-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2001-12</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -6947,12 +7132,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6977,104 +7162,90 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2001-12-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2001-12</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>0.002125693624458129</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ43" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS43" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -7101,17 +7272,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -7150,34 +7321,17 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>Hundaæði</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -7185,64 +7339,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD44" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG44" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN44" t="b">
-        <v>1</v>
-      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -7260,7 +7356,7 @@
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
         </is>
       </c>
       <c r="AT44" t="n">
@@ -7273,42 +7369,42 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -7335,17 +7431,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7384,76 +7480,165 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN45" t="b">
+        <v>1</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS45" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -7515,12 +7700,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2002-02-01</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2002-02</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7628,17 +7813,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7663,12 +7848,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2002-02-01</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2002-02</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -7677,76 +7862,170 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Hundaæði</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN47" t="b">
+        <v>0</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR47" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS47" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_RABI_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -7778,12 +8057,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7808,21 +8087,18 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2002-03-01</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2002-03</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
@@ -7859,42 +8135,42 @@
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -7926,12 +8202,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7956,18 +8232,21 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2002-03-01</t>
+          <t>2002-02-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2002-03</t>
+          <t>2002-02</t>
         </is>
       </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
       <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
@@ -8004,42 +8283,42 @@
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8071,12 +8350,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -8101,21 +8380,18 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2002-04-01</t>
+          <t>2002-02-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2002-02</t>
         </is>
       </c>
       <c r="N50" t="n">
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
@@ -8152,42 +8428,42 @@
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -8219,12 +8495,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -8249,18 +8525,21 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2002-04-01</t>
+          <t>2002-03-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2002-03</t>
         </is>
       </c>
       <c r="N51" t="n">
         <v>0</v>
       </c>
       <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
@@ -8297,42 +8576,42 @@
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8643,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -8394,21 +8673,18 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2002-05-01</t>
+          <t>2002-03-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2002-05</t>
+          <t>2002-03</t>
         </is>
       </c>
       <c r="N52" t="n">
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
@@ -8445,42 +8721,42 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -8512,12 +8788,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -8542,18 +8818,21 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2002-05-01</t>
+          <t>2002-04-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2002-05</t>
+          <t>2002-04</t>
         </is>
       </c>
       <c r="N53" t="n">
         <v>0</v>
       </c>
       <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
@@ -8590,42 +8869,42 @@
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8657,12 +8936,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -8687,21 +8966,18 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2002-06-01</t>
+          <t>2002-04-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2002-06</t>
+          <t>2002-04</t>
         </is>
       </c>
       <c r="N54" t="n">
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
@@ -8738,42 +9014,42 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -8805,12 +9081,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -8835,22 +9111,25 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2002-06-01</t>
+          <t>2002-05-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2002-06</t>
+          <t>2002-05</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0.002114204216545633</v>
+        <v>0</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -8883,42 +9162,42 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8950,12 +9229,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -8980,21 +9259,18 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2002-07-01</t>
+          <t>2002-05-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2002-07</t>
+          <t>2002-05</t>
         </is>
       </c>
       <c r="N56" t="n">
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
@@ -9031,42 +9307,42 @@
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -9098,12 +9374,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -9128,18 +9404,21 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2002-07-01</t>
+          <t>2002-06-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2002-07</t>
+          <t>2002-06</t>
         </is>
       </c>
       <c r="N57" t="n">
         <v>0</v>
       </c>
       <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
@@ -9176,42 +9455,42 @@
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -9243,12 +9522,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -9273,25 +9552,22 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2002-08-01</t>
+          <t>2002-06-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2002-08</t>
+          <t>2002-06</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>0.002114204216545633</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -9324,42 +9600,42 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -9391,12 +9667,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -9421,18 +9697,21 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2002-08-01</t>
+          <t>2002-07-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2002-08</t>
+          <t>2002-07</t>
         </is>
       </c>
       <c r="N59" t="n">
         <v>0</v>
       </c>
       <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
@@ -9469,42 +9748,42 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -9536,12 +9815,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -9566,21 +9845,18 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2002-09-01</t>
+          <t>2002-07-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2002-09</t>
+          <t>2002-07</t>
         </is>
       </c>
       <c r="N60" t="n">
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
@@ -9617,42 +9893,42 @@
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -9684,12 +9960,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -9714,18 +9990,21 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2002-09-01</t>
+          <t>2002-08-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2002-09</t>
+          <t>2002-08</t>
         </is>
       </c>
       <c r="N61" t="n">
         <v>0</v>
       </c>
       <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
@@ -9762,42 +10041,42 @@
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -9829,12 +10108,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -9859,21 +10138,18 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2002-10-01</t>
+          <t>2002-08-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2002-10</t>
+          <t>2002-08</t>
         </is>
       </c>
       <c r="N62" t="n">
         <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
@@ -9910,42 +10186,42 @@
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -9977,12 +10253,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -10007,18 +10283,21 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2002-10-01</t>
+          <t>2002-09-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2002-10</t>
+          <t>2002-09</t>
         </is>
       </c>
       <c r="N63" t="n">
         <v>0</v>
       </c>
       <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
@@ -10055,42 +10334,42 @@
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10401,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -10152,21 +10431,18 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2002-11-01</t>
+          <t>2002-09-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2002-11</t>
+          <t>2002-09</t>
         </is>
       </c>
       <c r="N64" t="n">
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
@@ -10203,42 +10479,42 @@
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -10270,12 +10546,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -10300,18 +10576,21 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2002-11-01</t>
+          <t>2002-10-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2002-11</t>
+          <t>2002-10</t>
         </is>
       </c>
       <c r="N65" t="n">
         <v>0</v>
       </c>
       <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
@@ -10348,42 +10627,42 @@
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -10415,12 +10694,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -10445,21 +10724,18 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2002-12-01</t>
+          <t>2002-10-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2002-12</t>
+          <t>2002-10</t>
         </is>
       </c>
       <c r="N66" t="n">
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
@@ -10496,42 +10772,42 @@
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -10563,12 +10839,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -10593,18 +10869,21 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2002-12-01</t>
+          <t>2002-11-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2002-12</t>
+          <t>2002-11</t>
         </is>
       </c>
       <c r="N67" t="n">
         <v>0</v>
       </c>
       <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
@@ -10641,42 +10920,42 @@
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -10708,12 +10987,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -10738,21 +11017,18 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2002-11-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2002-11</t>
         </is>
       </c>
       <c r="N68" t="n">
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
@@ -10789,42 +11065,42 @@
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -10856,12 +11132,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -10886,12 +11162,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2002-12-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2002-12</t>
         </is>
       </c>
       <c r="N69" t="n">
@@ -10900,6 +11176,9 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -10908,82 +11187,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ69" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS69" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -11010,17 +11275,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -11045,12 +11310,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2002-12-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2002-12</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -11059,165 +11324,76 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>Hundaæði</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD70" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE70" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF70" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG70" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN70" t="b">
-        <v>1</v>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ70" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS70" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -11249,12 +11425,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -11288,81 +11464,95 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>0.00314105057210781</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS71" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11389,17 +11579,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -11424,93 +11614,179 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2003-02-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2003-02</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN72" t="b">
+        <v>1</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11542,12 +11818,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -11572,22 +11848,25 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2003-02-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2003-02</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>0.002104635732751713</v>
+        <v>0</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -11620,42 +11899,42 @@
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -11682,17 +11961,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -11717,12 +11996,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2003-03-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2003-03</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -11731,79 +12010,170 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Hundaæði</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN74" t="b">
+        <v>0</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR74" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_RABI_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -11865,12 +12235,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2003-03-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2003-03</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -12010,12 +12380,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2003-04-01</t>
+          <t>2003-02-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2003-04</t>
+          <t>2003-02</t>
         </is>
       </c>
       <c r="N76" t="n">
@@ -12158,22 +12528,22 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2003-04-01</t>
+          <t>2003-02-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2003-04</t>
+          <t>2003-02</t>
         </is>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>0.002104635732751713</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -12303,12 +12673,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2003-05-01</t>
+          <t>2003-03-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2003-05</t>
+          <t>2003-03</t>
         </is>
       </c>
       <c r="N78" t="n">
@@ -12451,22 +12821,22 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2003-05-01</t>
+          <t>2003-03-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2003-05</t>
+          <t>2003-03</t>
         </is>
       </c>
       <c r="N79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>0.002104635732751713</v>
+        <v>0</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -12596,12 +12966,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2003-06-01</t>
+          <t>2003-04-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2003-06</t>
+          <t>2003-04</t>
         </is>
       </c>
       <c r="N80" t="n">
@@ -12744,12 +13114,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2003-06-01</t>
+          <t>2003-04-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2003-06</t>
+          <t>2003-04</t>
         </is>
       </c>
       <c r="N81" t="n">
@@ -12889,12 +13259,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>2003-05-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2003-07</t>
+          <t>2003-05</t>
         </is>
       </c>
       <c r="N82" t="n">
@@ -13037,22 +13407,22 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>2003-05-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2003-07</t>
+          <t>2003-05</t>
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>0.002104635732751713</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -13182,12 +13552,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2003-08-01</t>
+          <t>2003-06-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2003-08</t>
+          <t>2003-06</t>
         </is>
       </c>
       <c r="N84" t="n">
@@ -13330,12 +13700,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2003-08-01</t>
+          <t>2003-06-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2003-08</t>
+          <t>2003-06</t>
         </is>
       </c>
       <c r="N85" t="n">
@@ -13475,12 +13845,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2003-09-01</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2003-09</t>
+          <t>2003-07</t>
         </is>
       </c>
       <c r="N86" t="n">
@@ -13623,12 +13993,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2003-09-01</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2003-09</t>
+          <t>2003-07</t>
         </is>
       </c>
       <c r="N87" t="n">
@@ -13768,12 +14138,12 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2003-08-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2003-10</t>
+          <t>2003-08</t>
         </is>
       </c>
       <c r="N88" t="n">
@@ -13916,12 +14286,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2003-08-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2003-10</t>
+          <t>2003-08</t>
         </is>
       </c>
       <c r="N89" t="n">
@@ -14061,12 +14431,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2003-09-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2003-11</t>
+          <t>2003-09</t>
         </is>
       </c>
       <c r="N90" t="n">
@@ -14209,12 +14579,12 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2003-09-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2003-11</t>
+          <t>2003-09</t>
         </is>
       </c>
       <c r="N91" t="n">
@@ -14354,12 +14724,12 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2003-12</t>
+          <t>2003-10</t>
         </is>
       </c>
       <c r="N92" t="n">
@@ -14502,12 +14872,12 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2003-12</t>
+          <t>2003-10</t>
         </is>
       </c>
       <c r="N93" t="n">
@@ -14647,12 +15017,12 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2003-11</t>
         </is>
       </c>
       <c r="N94" t="n">
@@ -14765,12 +15135,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -14795,12 +15165,12 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2003-11</t>
         </is>
       </c>
       <c r="N95" t="n">
@@ -14817,82 +15187,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ95" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -14919,17 +15275,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -14954,12 +15310,12 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2003-12-01</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2003-12</t>
         </is>
       </c>
       <c r="N96" t="n">
@@ -14968,165 +15324,79 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>Hundaæði</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD96" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE96" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF96" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG96" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN96" t="b">
-        <v>1</v>
+      <c r="Q96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ96" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS96" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -15188,12 +15458,12 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2003-12-01</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2003-12</t>
         </is>
       </c>
       <c r="N97" t="n">
@@ -15303,12 +15573,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -15333,12 +15603,12 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2004-02-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2004-02</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N98" t="n">
@@ -15347,9 +15617,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -15358,68 +15625,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15446,17 +15727,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -15481,12 +15762,12 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2004-02-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2004-02</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N99" t="n">
@@ -15495,76 +15776,165 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="R99" t="n">
-        <v>0</v>
-      </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN99" t="b">
+        <v>1</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15626,12 +15996,12 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2004-03</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N100" t="n">
@@ -15739,17 +16109,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -15774,12 +16144,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2004-03</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N101" t="n">
@@ -15788,76 +16158,170 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="R101" t="n">
-        <v>0</v>
-      </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Hundaæði</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN101" t="b">
+        <v>0</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR101" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_RABI_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -15889,12 +16353,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -15919,21 +16383,18 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2004-04-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2004-04</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N102" t="n">
         <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q102" t="n">
         <v>0</v>
       </c>
       <c r="R102" t="n">
@@ -15970,42 +16431,42 @@
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -16037,12 +16498,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -16067,18 +16528,21 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2004-04-01</t>
+          <t>2004-02-01</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2004-04</t>
+          <t>2004-02</t>
         </is>
       </c>
       <c r="N103" t="n">
         <v>0</v>
       </c>
       <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
@@ -16115,42 +16579,42 @@
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -16182,12 +16646,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -16212,21 +16676,18 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2004-05-01</t>
+          <t>2004-02-01</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-02</t>
         </is>
       </c>
       <c r="N104" t="n">
         <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q104" t="n">
         <v>0</v>
       </c>
       <c r="R104" t="n">
@@ -16263,42 +16724,42 @@
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -16330,12 +16791,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -16360,22 +16821,25 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2004-05-01</t>
+          <t>2004-03-01</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-03</t>
         </is>
       </c>
       <c r="N105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>0.002096564599647205</v>
+        <v>0</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -16408,42 +16872,42 @@
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -16475,12 +16939,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -16505,21 +16969,18 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2004-06-01</t>
+          <t>2004-03-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2004-03</t>
         </is>
       </c>
       <c r="N106" t="n">
         <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q106" t="n">
         <v>0</v>
       </c>
       <c r="R106" t="n">
@@ -16556,42 +17017,42 @@
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -16623,12 +17084,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -16653,18 +17114,21 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2004-06-01</t>
+          <t>2004-04-01</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2004-04</t>
         </is>
       </c>
       <c r="N107" t="n">
         <v>0</v>
       </c>
       <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
         <v>0</v>
       </c>
       <c r="R107" t="n">
@@ -16701,42 +17165,42 @@
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -16768,12 +17232,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -16798,21 +17262,18 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2004-07-01</t>
+          <t>2004-04-01</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2004-07</t>
+          <t>2004-04</t>
         </is>
       </c>
       <c r="N108" t="n">
         <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q108" t="n">
         <v>0</v>
       </c>
       <c r="R108" t="n">
@@ -16849,42 +17310,42 @@
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -16916,12 +17377,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -16946,18 +17407,21 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2004-07-01</t>
+          <t>2004-05-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2004-07</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N109" t="n">
         <v>0</v>
       </c>
       <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="n">
         <v>0</v>
       </c>
       <c r="R109" t="n">
@@ -16994,42 +17458,42 @@
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -17061,12 +17525,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -17091,25 +17555,22 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2004-05-01</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2004-08</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O110" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>0.002096564599647205</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -17142,42 +17603,42 @@
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17209,12 +17670,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -17239,18 +17700,21 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2004-06-01</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2004-08</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N111" t="n">
         <v>0</v>
       </c>
       <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="n">
         <v>0</v>
       </c>
       <c r="R111" t="n">
@@ -17287,42 +17751,42 @@
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -17354,12 +17818,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -17384,21 +17848,18 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2004-09-01</t>
+          <t>2004-06-01</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2004-09</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N112" t="n">
         <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
@@ -17435,42 +17896,42 @@
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17502,12 +17963,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -17532,18 +17993,21 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2004-09-01</t>
+          <t>2004-07-01</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2004-09</t>
+          <t>2004-07</t>
         </is>
       </c>
       <c r="N113" t="n">
         <v>0</v>
       </c>
       <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
         <v>0</v>
       </c>
       <c r="R113" t="n">
@@ -17580,42 +18044,42 @@
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -17647,12 +18111,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -17677,21 +18141,18 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2004-10-01</t>
+          <t>2004-07-01</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2004-10</t>
+          <t>2004-07</t>
         </is>
       </c>
       <c r="N114" t="n">
         <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
@@ -17728,42 +18189,42 @@
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17795,12 +18256,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -17825,18 +18286,21 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2004-10-01</t>
+          <t>2004-08-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2004-10</t>
+          <t>2004-08</t>
         </is>
       </c>
       <c r="N115" t="n">
         <v>0</v>
       </c>
       <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
@@ -17873,42 +18337,42 @@
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -17940,12 +18404,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -17970,21 +18434,18 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2004-11-01</t>
+          <t>2004-08-01</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2004-11</t>
+          <t>2004-08</t>
         </is>
       </c>
       <c r="N116" t="n">
         <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
@@ -18021,42 +18482,42 @@
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -18088,12 +18549,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -18118,18 +18579,21 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2004-11-01</t>
+          <t>2004-09-01</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2004-11</t>
+          <t>2004-09</t>
         </is>
       </c>
       <c r="N117" t="n">
         <v>0</v>
       </c>
       <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
@@ -18166,42 +18630,42 @@
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -18233,12 +18697,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -18263,21 +18727,18 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-09-01</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2004-09</t>
         </is>
       </c>
       <c r="N118" t="n">
         <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
@@ -18314,42 +18775,42 @@
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -18381,12 +18842,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -18411,18 +18872,21 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-10-01</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2004-10</t>
         </is>
       </c>
       <c r="N119" t="n">
         <v>0</v>
       </c>
       <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
@@ -18459,40 +18923,771 @@
       </c>
       <c r="AV119" t="inlineStr">
         <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC119" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2004-10-01</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2004-10</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr"/>
+      <c r="AT120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV120" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW119" t="inlineStr">
+      <c r="AW120" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX119" t="inlineStr">
+      <c r="AX120" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY119" t="inlineStr">
+      <c r="AY120" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ119" t="inlineStr">
+      <c r="AZ120" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA119" t="inlineStr">
+      <c r="BA120" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB119" t="inlineStr">
+      <c r="BB120" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC119" t="inlineStr">
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2004-11-01</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2004-11</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP121" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr"/>
+      <c r="AT121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC121" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2004-11-01</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2004-11</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr"/>
+      <c r="AT122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2004-12-01</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2004-12</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr"/>
+      <c r="AT123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2004-12-01</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2004-12</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr"/>
+      <c r="AT124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -18624,7 +19819,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11">
@@ -18644,7 +19839,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -18654,7 +19849,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -18676,7 +19871,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
